--- a/data/Barrister_Master.xlsx
+++ b/data/Barrister_Master.xlsx
@@ -904,10 +904,10 @@
         <v>Completed Service Events</v>
       </c>
       <c r="B2" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C2" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="15" hidden="0" customHeight="1">
@@ -926,10 +926,10 @@
         <v>Total Timeline Positions</v>
       </c>
       <c r="B4" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C4" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="15" hidden="0" customHeight="1">
@@ -937,10 +937,10 @@
         <v>Completed Unique Clients</v>
       </c>
       <c r="B5" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="15" hidden="0" customHeight="1">
@@ -948,10 +948,10 @@
         <v>Forward-Looking Client Count</v>
       </c>
       <c r="B6" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="15" hidden="0" customHeight="1">
@@ -1027,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" hidden="0" customWidth="1"/>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fallston</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Part 2</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TJ Maxx</t>
+          <t>Dunkin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Fallston</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>TJX Project</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -4215,27 +4215,137 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>TJ Maxx</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>TJX</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Giant Food Stores</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Olney</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Maryland</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>WeWork</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Server install</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Hebrew Home of Greater Washington</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>North Bethesda</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Printer</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4395,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
@@ -5264,7 +5374,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5852,7 +5962,7 @@
         </is>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5888,6 +5998,34 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WeWork</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>71</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
@@ -5950,7 +6088,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30, 34, 39, 61, 62, 66, 68</t>
+          <t>30, 34, 39, 61, 62, 66, 69</t>
         </is>
       </c>
     </row>
@@ -5972,7 +6110,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marshalls</t>
+          <t>Dunkin</t>
         </is>
       </c>
       <c r="B4">
@@ -5980,44 +6118,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35, 44, 46, 63, 64</t>
+          <t>56, 58, 59, 67, 68</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dunkin</t>
+          <t>Hebrew Home of Greater Washington</t>
         </is>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56, 58, 59, 67</t>
+          <t>8, 33, 48, 51, 72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Giant Food Stores</t>
+          <t>Marshalls</t>
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10, 20, 50, 69</t>
+          <t>35, 44, 46, 63, 64</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hebrew Home of Greater Washington</t>
+          <t>Giant Food Stores</t>
         </is>
       </c>
       <c r="B7">
@@ -6025,7 +6163,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8, 33, 48, 51</t>
+          <t>10, 20, 50, 70</t>
         </is>
       </c>
     </row>
@@ -6272,13 +6410,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -6288,13 +6426,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -6355,7 +6493,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
@@ -6665,6 +6803,33 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>TJX Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Autumn Lake</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Glen Burnie, MD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Printer</t>
         </is>
       </c>
     </row>
@@ -7026,10 +7191,10 @@
         <v>Completed Service Events</v>
       </c>
       <c r="B2" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C2" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="15" hidden="0" customHeight="1">
@@ -7037,10 +7202,10 @@
         <v>Completed Unique Clients</v>
       </c>
       <c r="B3" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="15" hidden="0" customHeight="1">
@@ -7048,10 +7213,10 @@
         <v>Forward-Looking Client Count</v>
       </c>
       <c r="B4" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="15" hidden="0" customHeight="1">
@@ -7059,10 +7224,10 @@
         <v>Timeline Max Position</v>
       </c>
       <c r="B5" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="15" hidden="0" customHeight="1">

--- a/data/Barrister_Master.xlsx
+++ b/data/Barrister_Master.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client List" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4703,7 +4704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4773,10 +4774,110 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Source: derived from the Service Events sheet of Barrister_Source_of_Truth_Master_Verified_Through_Event84_2026-07-26.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled Timeline Entries</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline sheet (currently empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Completed Unique Clients</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Client List (derived from Service Events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Forward-Looking Client Count</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Client List (derived from Service Events)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Visit #</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Date / Timing</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>

--- a/data/Barrister_Master.xlsx
+++ b/data/Barrister_Master.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,7 +545,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>90</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -588,7 +588,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>344</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,7 +631,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>344</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -674,7 +674,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>180</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -717,7 +717,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>50</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>180</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -803,7 +803,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -846,7 +846,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>45</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,7 +889,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>135</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -932,7 +932,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>212.5</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -975,7 +975,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>157.5</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1018,7 +1018,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>85</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1061,7 +1061,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>50</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1104,7 +1104,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>25</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1147,7 +1147,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>75</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1190,7 +1190,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>45</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1233,7 +1233,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>50</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1276,7 +1276,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>106.67</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1319,7 +1319,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>153.33</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1362,7 +1362,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>112.5</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1405,7 +1405,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>97.91</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1448,7 +1448,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>50</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1491,7 +1491,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>50</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>200</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>50</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1620,7 +1620,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>175</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1663,7 +1663,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>320</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1706,7 +1706,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>320</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1749,7 +1749,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>200</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1792,7 +1792,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>96.66</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1835,7 +1835,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>140</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1878,7 +1878,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>25</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1921,7 +1921,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>50</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1964,7 +1964,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>70</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2007,7 +2007,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>70</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2050,7 +2050,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>65</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2093,7 +2093,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I38">
+      <c r="I38" t="n">
         <v>90</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2136,7 +2136,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I39">
+      <c r="I39" t="n">
         <v>240</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2179,7 +2179,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I40">
+      <c r="I40" t="n">
         <v>90</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2222,7 +2222,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I41">
+      <c r="I41" t="n">
         <v>60</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2265,7 +2265,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I42">
+      <c r="I42" t="n">
         <v>45</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2308,7 +2308,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I43">
+      <c r="I43" t="n">
         <v>50</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2351,7 +2351,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I44">
+      <c r="I44" t="n">
         <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2394,7 +2394,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I45">
+      <c r="I45" t="n">
         <v>123.75</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2437,7 +2437,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I46">
+      <c r="I46" t="n">
         <v>128</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2480,7 +2480,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I47">
+      <c r="I47" t="n">
         <v>90</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2523,7 +2523,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I48">
+      <c r="I48" t="n">
         <v>130</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2566,7 +2566,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I49">
+      <c r="I49" t="n">
         <v>70</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2609,7 +2609,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I50">
+      <c r="I50" t="n">
         <v>90</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2652,7 +2652,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I51">
+      <c r="I51" t="n">
         <v>50</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2695,7 +2695,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I52">
+      <c r="I52" t="n">
         <v>60</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2738,7 +2738,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I53">
+      <c r="I53" t="n">
         <v>116.24</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2781,7 +2781,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I54">
+      <c r="I54" t="n">
         <v>132.03</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2824,7 +2824,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I55">
+      <c r="I55" t="n">
         <v>120</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2867,7 +2867,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I56">
+      <c r="I56" t="n">
         <v>120</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2910,7 +2910,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I57">
+      <c r="I57" t="n">
         <v>170.66</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2953,8 +2953,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I58">
-        <v>66.74</v>
+      <c r="I58" t="n">
+        <v>66.73999999999999</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2996,7 +2996,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I59">
+      <c r="I59" t="n">
         <v>202.5</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3039,7 +3039,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I60">
+      <c r="I60" t="n">
         <v>250</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3122,7 +3122,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I62">
+      <c r="I62" t="n">
         <v>194.99</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3165,7 +3165,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I63">
+      <c r="I63" t="n">
         <v>100.83</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3303,7 +3303,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I66">
+      <c r="I66" t="n">
         <v>129.16</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3396,7 +3396,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I68">
+      <c r="I68" t="n">
         <v>183.74</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I69">
+      <c r="I69" t="n">
         <v>350</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3482,7 +3482,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I70">
+      <c r="I70" t="n">
         <v>180</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3525,7 +3525,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I71">
+      <c r="I71" t="n">
         <v>103.33</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3573,7 +3573,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I72">
+      <c r="I72" t="n">
         <v>90</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3616,7 +3616,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I73">
+      <c r="I73" t="n">
         <v>50</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3664,7 +3664,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I74">
+      <c r="I74" t="n">
         <v>180</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3712,7 +3712,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I75">
+      <c r="I75" t="n">
         <v>50</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3760,7 +3760,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I76">
+      <c r="I76" t="n">
         <v>50</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3803,7 +3803,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I77">
+      <c r="I77" t="n">
         <v>120</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3886,7 +3886,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I79">
+      <c r="I79" t="n">
         <v>160.29</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3934,7 +3934,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I80">
+      <c r="I80" t="n">
         <v>168.75</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3982,7 +3982,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I81">
+      <c r="I81" t="n">
         <v>163.33</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4025,7 +4025,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I82">
+      <c r="I82" t="n">
         <v>125</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4068,7 +4068,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I83">
+      <c r="I83" t="n">
         <v>110</v>
       </c>
       <c r="J83" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4116,7 +4116,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I84">
+      <c r="I84" t="n">
         <v>65</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4270,6 +4270,41 @@
         </is>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dunkin</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Reisterstown</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4333,10 +4368,10 @@
           <t>TJ Maxx</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -4361,10 +4396,10 @@
           <t>Marshalls</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4389,10 +4424,10 @@
           <t>USDA</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>24</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4417,10 +4452,10 @@
           <t>Dunkin</t>
         </is>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
         <v>56</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4445,10 +4480,10 @@
           <t>Giant Food Stores</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4473,10 +4508,10 @@
           <t>Hebrew Home of Greater Washington</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4501,10 +4536,10 @@
           <t>7-Eleven</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4529,10 +4564,10 @@
           <t>HomeGoods</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>22</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4557,10 +4592,10 @@
           <t>Macy's</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4585,10 +4620,10 @@
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>3</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -4613,10 +4648,10 @@
           <t>Verizon</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -4641,10 +4676,10 @@
           <t>Bloomingdale's</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -4669,10 +4704,10 @@
           <t>Hampton Inn &amp; Suites</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>2</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -4697,10 +4732,10 @@
           <t>Weis Markets</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -4725,10 +4760,10 @@
           <t>Residential – Annapolis Neck, MD</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -4753,10 +4788,10 @@
           <t>Under Armour</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>2</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>18</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -4781,10 +4816,10 @@
           <t>Hilton Garden Inn</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>2</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>32</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -4809,10 +4844,10 @@
           <t>Montpelier Liquors</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>2</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>45</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -4837,10 +4872,10 @@
           <t>Office of MD Senator Angela Alsobrooks</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>2</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>47</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4865,10 +4900,10 @@
           <t>Carvana</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>60</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4893,10 +4928,10 @@
           <t>Autumn Lake Healthcare</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>2</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>74</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4921,10 +4956,10 @@
           <t>Davis Polk &amp; Wardwell</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4949,10 +4984,10 @@
           <t>Office of MD Senator Chris Van Hollen</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4977,10 +5012,10 @@
           <t>Atrium Village</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>16</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5005,10 +5040,10 @@
           <t>Maryland Baptist Age Home</t>
         </is>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>17</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5033,10 +5068,10 @@
           <t>Joint Base Andrews</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5061,10 +5096,10 @@
           <t>PepsiCo</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>1</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5089,10 +5124,10 @@
           <t>Baskin-Robbins</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>41</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -5117,10 +5152,10 @@
           <t>WeWork</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>2</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>71</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,10 +5180,10 @@
           <t>Miramar</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>72</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -5173,10 +5208,10 @@
           <t>Homesense</t>
         </is>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>73</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -5201,7 +5236,7 @@
           <t>Source: derived from the Service Events sheet of Barrister_Source_of_Truth_Master_Verified_Through_Event84_2026-07-26.xlsx</t>
         </is>
       </c>
-      <c r="B33">
+      <c r="B33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5247,11 +5282,11 @@
           <t>Completed Service Events</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2">
-        <v>87</v>
+      <c r="B2" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -5260,10 +5295,10 @@
           <t>Jurisdictions Covered</t>
         </is>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5273,24 +5308,23 @@
           <t>Total Timeline Positions</t>
         </is>
       </c>
-      <c r="B4" s="2">
-        <v>87</v>
-      </c>
-      <c r="C4" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="B4" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>88</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Source: derived from the Service Events sheet of Barrister_Source_of_Truth_Master_Verified_Through_Event84_2026-07-26.xlsx</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5300,10 +5334,10 @@
           <t>Scheduled Timeline Entries</t>
         </is>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="n">
         <v>31</v>
       </c>
     </row>
@@ -5313,10 +5347,10 @@
           <t>Completed Unique Clients</t>
         </is>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="2" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5346,7 +5380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5358,32 +5392,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Visit #</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date / Timing</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5397,12 +5431,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reisterstown, MD</t>
+          <t>Timonium, MD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5414,17 +5448,17 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dunkin</t>
+          <t>Marshalls</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Timonium, MD</t>
+          <t>Owings Mills, MD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5441,12 +5475,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owings Mills, MD</t>
+          <t>Annapolis, MD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5458,20 +5492,42 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
+          <t>Eastern Shore Warehouse</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sparrows Point, MD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Marshalls</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annapolis, MD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Frederick, MD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>

--- a/data/Barrister_Master.xlsx
+++ b/data/Barrister_Master.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,7 +545,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>90</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -588,7 +588,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>344</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,7 +631,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>344</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -674,7 +674,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>180</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -717,7 +717,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>50</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>180</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -803,7 +803,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>50</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -846,7 +846,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>45</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,7 +889,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>135</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -932,7 +932,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>212.5</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -975,7 +975,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>157.5</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1018,7 +1018,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>85</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1061,7 +1061,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>50</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1104,7 +1104,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>25</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1147,7 +1147,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>75</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1190,7 +1190,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>45</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1233,7 +1233,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>50</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1276,7 +1276,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>106.67</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1319,7 +1319,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>153.33</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1362,7 +1362,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>112.5</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1405,7 +1405,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>97.91</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1448,7 +1448,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>50</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1491,7 +1491,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>50</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>200</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1577,7 +1577,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>50</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1620,7 +1620,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>175</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1663,7 +1663,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>320</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1706,7 +1706,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>320</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1749,7 +1749,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>200</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1792,7 +1792,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>96.66</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1835,7 +1835,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>140</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1878,7 +1878,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>25</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1921,7 +1921,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>50</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1964,7 +1964,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>70</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2007,7 +2007,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>70</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2050,7 +2050,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>65</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2093,7 +2093,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>90</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2136,7 +2136,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>240</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2179,7 +2179,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>90</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2222,7 +2222,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>60</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2265,7 +2265,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>45</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2308,7 +2308,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>50</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2351,7 +2351,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2394,7 +2394,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>123.75</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2437,7 +2437,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>128</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2480,7 +2480,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>90</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2523,7 +2523,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>130</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2566,7 +2566,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>70</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2609,7 +2609,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>90</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2652,7 +2652,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>50</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2695,7 +2695,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>60</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2738,7 +2738,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>116.24</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2781,7 +2781,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>132.03</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2824,7 +2824,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>120</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2867,7 +2867,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>120</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2910,7 +2910,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>170.66</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2953,8 +2953,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>66.73999999999999</v>
+      <c r="I58">
+        <v>66.74</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2996,7 +2996,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>202.5</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3039,7 +3039,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>250</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3122,7 +3122,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>194.99</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3165,7 +3165,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>100.83</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3303,7 +3303,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>129.16</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3396,7 +3396,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>183.74</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3439,7 +3439,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>350</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3482,7 +3482,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>180</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3525,7 +3525,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>103.33</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3573,7 +3573,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>90</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3616,7 +3616,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>50</v>
       </c>
       <c r="J73" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3664,7 +3664,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>180</v>
       </c>
       <c r="J74" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3712,7 +3712,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>50</v>
       </c>
       <c r="J75" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3760,7 +3760,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>50</v>
       </c>
       <c r="J76" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3803,7 +3803,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>120</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3886,7 +3886,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>160.29</v>
       </c>
       <c r="J79" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3934,7 +3934,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>168.75</v>
       </c>
       <c r="J80" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3982,7 +3982,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>163.33</v>
       </c>
       <c r="J81" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4025,7 +4025,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>125</v>
       </c>
       <c r="J82" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4068,7 +4068,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>110</v>
       </c>
       <c r="J83" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4116,7 +4116,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>65</v>
       </c>
       <c r="J84" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -4305,6 +4305,76 @@
         </is>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Eastern Shore Warehouse</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sparrows Point</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Giant Food Stores</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Severna Park</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
@@ -4321,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4368,10 +4438,10 @@
           <t>TJ Maxx</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>8</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -4396,10 +4466,10 @@
           <t>Marshalls</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>9</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4424,10 +4494,10 @@
           <t>USDA</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>24</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4452,10 +4522,10 @@
           <t>Dunkin</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>8</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>56</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4480,10 +4550,10 @@
           <t>Giant Food Stores</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
         <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4508,10 +4578,10 @@
           <t>Hebrew Home of Greater Washington</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4536,10 +4606,10 @@
           <t>7-Eleven</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4564,10 +4634,10 @@
           <t>HomeGoods</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>22</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4592,10 +4662,10 @@
           <t>Macy's</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4620,10 +4690,10 @@
           <t>Food Lion</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>3</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -4648,10 +4718,10 @@
           <t>Verizon</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -4676,10 +4746,10 @@
           <t>Bloomingdale's</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -4704,10 +4774,10 @@
           <t>Hampton Inn &amp; Suites</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -4732,10 +4802,10 @@
           <t>Weis Markets</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>12</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -4760,10 +4830,10 @@
           <t>Residential – Annapolis Neck, MD</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -4788,10 +4858,10 @@
           <t>Under Armour</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>18</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -4816,10 +4886,10 @@
           <t>Hilton Garden Inn</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>32</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -4844,10 +4914,10 @@
           <t>Montpelier Liquors</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>45</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -4872,10 +4942,10 @@
           <t>Office of MD Senator Angela Alsobrooks</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>47</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4900,10 +4970,10 @@
           <t>Carvana</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>60</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4928,10 +4998,10 @@
           <t>Autumn Lake Healthcare</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>74</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4956,10 +5026,10 @@
           <t>Davis Polk &amp; Wardwell</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4984,10 +5054,10 @@
           <t>Office of MD Senator Chris Van Hollen</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>13</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -5012,10 +5082,10 @@
           <t>Atrium Village</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>16</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5040,10 +5110,10 @@
           <t>Maryland Baptist Age Home</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>17</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5068,10 +5138,10 @@
           <t>Joint Base Andrews</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5096,10 +5166,10 @@
           <t>PepsiCo</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5124,10 +5194,10 @@
           <t>Baskin-Robbins</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>41</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -5152,10 +5222,10 @@
           <t>WeWork</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>2</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>71</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -5180,10 +5250,10 @@
           <t>Miramar</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>72</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -5208,10 +5278,10 @@
           <t>Homesense</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>73</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -5236,8 +5306,36 @@
           <t>Source: derived from the Service Events sheet of Barrister_Source_of_Truth_Master_Verified_Through_Event84_2026-07-26.xlsx</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Eastern Shore Warehouse</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>89</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5282,11 +5380,11 @@
           <t>Completed Service Events</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>88</v>
+      <c r="B2" s="2">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2">
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -5295,11 +5393,11 @@
           <t>Jurisdictions Covered</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>6</v>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -5308,11 +5406,11 @@
           <t>Total Timeline Positions</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>88</v>
+      <c r="B4" s="2">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2">
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -5321,10 +5419,10 @@
           <t>Source: derived from the Service Events sheet of Barrister_Source_of_Truth_Master_Verified_Through_Event84_2026-07-26.xlsx</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
@@ -5334,11 +5432,11 @@
           <t>Scheduled Timeline Entries</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>31</v>
+      <c r="B7" s="2">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -5347,11 +5445,11 @@
           <t>Completed Unique Clients</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>32</v>
+      <c r="B8" s="2">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -5380,7 +5478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5492,17 +5590,17 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eastern Shore Warehouse</t>
+          <t>Marshalls</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sparrows Point, MD</t>
+          <t>Frederick, MD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5514,12 +5612,12 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marshalls</t>
+          <t>Dunkin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frederick, MD</t>
+          <t>Owings Mills, MD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5528,6 +5626,28 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Food Lion</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Essex, MD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
